--- a/reports/arsenal/军火榜_2026-09-02.xlsx
+++ b/reports/arsenal/军火榜_2026-09-02.xlsx
@@ -501,21 +501,21 @@
   <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
@@ -530,84 +530,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-02 · 共 22 个候选 · 按日均涨星降序(总星数偏袒老仓,日均涨星才看得出现在热不热)· 数据源 candidates.json</t>
+          <t>GitHub 军火榜 · 2026-09-02 · 共 22 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 数据源 candidates.json</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>总星数</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星数</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>落哪条产线</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>可吸收形式</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>许可类型</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>是否新发现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>总星数</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星来源</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>日均涨星</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>区间涨星</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>区间天数</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>原始描述</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>许可证</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>语言</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>许可证</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>许可类型</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>可吸收形式</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>落哪条产线</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>能做什么</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>原始描述</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>证据</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>是否新发现</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -662,58 +662,64 @@
           <t>subsy/skill-cabinet</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Skill 展示柜</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>https://github.com/subsy/skill-cabinet</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>328</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>skill-cabinet</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Skill 展示柜</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>skill-cabinet</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -760,62 +766,68 @@
           <t>jub0t/Concat</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>提供免费且开源的视频编辑替代品</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>https://github.com/jub0t/Concat</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Free &amp; Open-Source CapCut replacement</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>MPL-2.0</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>视频产线</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>提供免费且开源的视频编辑替代品</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -866,62 +878,68 @@
           <t>liyue-aigc/seedance-2-5-video-director</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>https://github.com/liyue-aigc/seedance-2-5-video-director</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="D5" s="5" t="n">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>16.93</v>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>视频产线</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -972,60 +990,66 @@
           <t>sindresorhus/awesome-nodejs</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>66678</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>提供 Node.js 包和资源的列表</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>https://github.com/sindresorhus/awesome-nodejs</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>66678</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>15.03</v>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Delightful Node.js packages and resources</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>提供 Node.js 包和资源的列表</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>Delightful Node.js packages and resources</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1074,62 +1098,68 @@
           <t>21st-dev/magic-mcp</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>5775</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>https://github.com/21st-dev/magic-mcp</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>5775</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>10.31</v>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>It's like v0, but in your Cursor / Claude Code / Windsurf</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1180,60 +1210,66 @@
           <t>steven2358/awesome-generative-ai</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>12552</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>提供现代生成式人工智能项目和服务的精选列表</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>https://github.com/steven2358/awesome-generative-ai</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>12552</v>
-      </c>
-      <c r="D8" s="5" t="n">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>提供现代生成式人工智能项目和服务的精选列表</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1282,62 +1318,68 @@
           <t>edoardottt/awesome-hacker-search-engines</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="n">
+        <v>11117</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>https://github.com/edoardottt/awesome-hacker-search-engines</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>11117</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>7.24</v>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>Shell</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1388,62 +1430,68 @@
           <t>Rzna-5559/Mrite</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="n">
+        <v>445</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>内置 Skill 的数模智能体</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>https://github.com/Rzna-5559/Mrite</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>445</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>5.24</v>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>全网最强数模智能体内置Skill</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>全网最强数模智能体内置Skill</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>TeX</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>内置 Skill 的数模智能体</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>全网最强数模智能体内置Skill</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>全网最强数模智能体内置Skill</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1490,62 +1538,68 @@
           <t>budtmo/docker-android</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="n">
+        <v>15799</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>提供 Android 在 Docker 中的解决方案，支持视频录制和 MCP 服务器</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>https://github.com/budtmo/docker-android</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>15799</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>4.46</v>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>提供 Android 在 Docker 中的解决方案，支持视频录制和 MCP 服务器</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1596,62 +1650,68 @@
           <t>scaccogatto/okf-skills</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="n">
+        <v>353</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>https://github.com/scaccogatto/okf-skills</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>353</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>4.41</v>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles.</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles.</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -1702,62 +1762,68 @@
           <t>ZeKaiNie/universal-examprep-skill</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude Agent Skill 的考试冲刺教练功能</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>https://github.com/ZeKaiNie/universal-examprep-skill</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>3.96</v>
       </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>Last-night exam-cram coach as a Claude Agent Skill</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude Agent Skill 的考试冲刺教练功能</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1808,62 +1874,68 @@
           <t>lgazo/drawio-mcp-server</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) 服务器</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>https://github.com/lgazo/drawio-mcp-server</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1455</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>2.92</v>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) Server</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) Server</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) 服务器</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -1910,60 +1982,66 @@
           <t>Calinou/awesome-godot</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="n">
+        <v>10677</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Godot 引擎插件、脚本和附加组件列表</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>https://github.com/Calinou/awesome-godot</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>10677</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>2.57</v>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>Godot 引擎插件、脚本和附加组件列表</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2012,62 +2090,68 @@
           <t>Taxuspt/garmin_mcp</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>访问 Garmin 数据的 MCP 服务器</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>https://github.com/Taxuspt/garmin_mcp</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>1102</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>2.03</v>
       </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>MCP server to access Garmin data</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>MCP server to access Garmin data</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>访问 Garmin 数据的 MCP 服务器</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2114,62 +2198,68 @@
           <t>yushui2022/MathModel-Skill</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>https://github.com/yushui2022/MathModel-Skill</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>332</v>
-      </c>
-      <c r="D17" s="5" t="n">
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>1.54</v>
       </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Agent-native mathematical modeling workflow skills</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2216,62 +2306,68 @@
           <t>realZillionX/InspireSkill</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>https://github.com/realZillionX/InspireSkill</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="D18" s="5" t="n">
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>1.49</v>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2318,62 +2414,68 @@
           <t>VkRainB/ccMesh</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>https://github.com/VkRainB/ccMesh</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="D19" s="5" t="n">
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code / Codex local AI proxy gateway desktop app</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Rust</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2424,62 +2526,68 @@
           <t>dodolalorc/astro-navfolio</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>提供基于 Astro 的个人发布主题</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>https://github.com/dodolalorc/astro-navfolio</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="D20" s="5" t="n">
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>A serene Astro theme for personal publishing</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>Astro</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>提供基于 Astro 的个人发布主题</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>A serene Astro theme for personal publishing</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -2530,62 +2638,68 @@
           <t>81NewArk/AntiCAP-WebApi</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>提供基于 AntiCAP 开发的多类型验证码识别网站</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>https://github.com/81NewArk/AntiCAP-WebApi</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>366</v>
-      </c>
-      <c r="D21" s="5" t="n">
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>基于AntiCAP开发的多类型验证码识别网站</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>HTML</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>提供基于 AntiCAP 开发的多类型验证码识别网站</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2632,60 +2746,66 @@
           <t>mikalv/awesome-qt-qml</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="n">
+        <v>2605</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Qt 和 QML 库、资源、项目列表</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>https://github.com/mikalv/awesome-qt-qml</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>2605</v>
-      </c>
-      <c r="D22" s="5" t="n">
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>Qt 和 QML 库、资源、项目列表</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2734,62 +2854,68 @@
           <t>curiositech/some_claude_skills</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude skills，简化生活操作</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>https://github.com/curiositech/some_claude_skills</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>209</v>
-      </c>
-      <c r="D23" s="5" t="n">
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
         <v>0.72</v>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Claude skills that make my life easier.</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Claude skills that make my life easier.</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude skills，简化生活操作</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -2836,60 +2962,66 @@
           <t>tmcw/awesome-geojson</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="n">
+        <v>2535</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON 工具库，简化操作</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>https://github.com/tmcw/awesome-geojson</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>2535</v>
-      </c>
-      <c r="D24" s="5" t="n">
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON utilities that will make your life easier.</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON utilities that will make your life easier.</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON 工具库，简化操作</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2950,21 +3082,21 @@
   <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
@@ -2986,77 +3118,77 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>总星数</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星数</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>落哪条产线</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>可吸收形式</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>许可类型</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>是否新发现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>总星数</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星来源</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>日均涨星</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>区间涨星</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>区间天数</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>原始描述</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>许可证</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>语言</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>许可证</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>许可类型</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>可吸收形式</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>落哪条产线</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>能做什么</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>原始描述</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>证据</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>是否新发现</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -3111,58 +3243,64 @@
           <t>subsy/skill-cabinet</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Skill 展示柜</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>https://github.com/subsy/skill-cabinet</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>328</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>skill-cabinet</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Skill 展示柜</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>skill-cabinet</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -3209,62 +3347,68 @@
           <t>jub0t/Concat</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>提供免费且开源的视频编辑替代品</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>https://github.com/jub0t/Concat</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Free &amp; Open-Source CapCut replacement</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>MPL-2.0</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>视频产线</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>提供免费且开源的视频编辑替代品</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -3315,62 +3459,68 @@
           <t>liyue-aigc/seedance-2-5-video-director</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>https://github.com/liyue-aigc/seedance-2-5-video-director</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="D5" s="5" t="n">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>16.93</v>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>视频产线</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -3421,60 +3571,66 @@
           <t>sindresorhus/awesome-nodejs</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>66678</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>提供 Node.js 包和资源的列表</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>https://github.com/sindresorhus/awesome-nodejs</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>66678</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>15.03</v>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Delightful Node.js packages and resources</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>提供 Node.js 包和资源的列表</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>Delightful Node.js packages and resources</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3523,62 +3679,68 @@
           <t>21st-dev/magic-mcp</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>5775</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>https://github.com/21st-dev/magic-mcp</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>5775</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>10.31</v>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>It's like v0, but in your Cursor / Claude Code / Windsurf</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -3629,60 +3791,66 @@
           <t>steven2358/awesome-generative-ai</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>12552</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>提供现代生成式人工智能项目和服务的精选列表</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>https://github.com/steven2358/awesome-generative-ai</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>12552</v>
-      </c>
-      <c r="D8" s="5" t="n">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>提供现代生成式人工智能项目和服务的精选列表</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3731,62 +3899,68 @@
           <t>edoardottt/awesome-hacker-search-engines</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="n">
+        <v>11117</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>https://github.com/edoardottt/awesome-hacker-search-engines</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>11117</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>7.24</v>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>Shell</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -3837,62 +4011,68 @@
           <t>scaccogatto/okf-skills</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="n">
+        <v>353</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>https://github.com/scaccogatto/okf-skills</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>353</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>4.41</v>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles.</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles.</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -3943,62 +4123,68 @@
           <t>ZeKaiNie/universal-examprep-skill</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude Agent Skill 的考试冲刺教练功能</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>https://github.com/ZeKaiNie/universal-examprep-skill</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>3.96</v>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Last-night exam-cram coach as a Claude Agent Skill</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude Agent Skill 的考试冲刺教练功能</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -4049,62 +4235,68 @@
           <t>lgazo/drawio-mcp-server</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) 服务器</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>https://github.com/lgazo/drawio-mcp-server</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>1455</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>2.92</v>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) Server</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) Server</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) 服务器</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -4151,62 +4343,68 @@
           <t>Taxuspt/garmin_mcp</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>访问 Garmin 数据的 MCP 服务器</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>https://github.com/Taxuspt/garmin_mcp</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>1102</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>2.03</v>
       </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>MCP server to access Garmin data</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>MCP server to access Garmin data</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>访问 Garmin 数据的 MCP 服务器</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -4253,62 +4451,68 @@
           <t>yushui2022/MathModel-Skill</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>https://github.com/yushui2022/MathModel-Skill</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>332</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>1.54</v>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Agent-native mathematical modeling workflow skills</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -4355,62 +4559,68 @@
           <t>realZillionX/InspireSkill</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>https://github.com/realZillionX/InspireSkill</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>1.49</v>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -4457,62 +4667,68 @@
           <t>VkRainB/ccMesh</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>https://github.com/VkRainB/ccMesh</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code / Codex local AI proxy gateway desktop app</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>Rust</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -4563,62 +4779,68 @@
           <t>dodolalorc/astro-navfolio</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>提供基于 Astro 的个人发布主题</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>https://github.com/dodolalorc/astro-navfolio</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="D17" s="5" t="n">
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>A serene Astro theme for personal publishing</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Astro</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>提供基于 Astro 的个人发布主题</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>A serene Astro theme for personal publishing</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -4669,62 +4891,68 @@
           <t>81NewArk/AntiCAP-WebApi</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>提供基于 AntiCAP 开发的多类型验证码识别网站</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>https://github.com/81NewArk/AntiCAP-WebApi</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>366</v>
-      </c>
-      <c r="D18" s="5" t="n">
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>基于AntiCAP开发的多类型验证码识别网站</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>HTML</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>提供基于 AntiCAP 开发的多类型验证码识别网站</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -4771,62 +4999,68 @@
           <t>curiositech/some_claude_skills</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude skills，简化生活操作</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>https://github.com/curiositech/some_claude_skills</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>209</v>
-      </c>
-      <c r="D19" s="5" t="n">
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>0.72</v>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Claude skills that make my life easier.</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Claude skills that make my life easier.</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude skills，简化生活操作</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -4873,60 +5107,66 @@
           <t>tmcw/awesome-geojson</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="n">
+        <v>2535</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON 工具库，简化操作</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>https://github.com/tmcw/awesome-geojson</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>2535</v>
-      </c>
-      <c r="D20" s="5" t="n">
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON utilities that will make your life easier.</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON utilities that will make your life easier.</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON 工具库，简化操作</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4987,21 +5227,21 @@
   <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
@@ -5016,84 +5256,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>可用在【视频产线】的候选 · 共 2 个 · 按日均涨星降序</t>
+          <t>可用在【视频产线】的候选 · 共 2 个 · 按周涨星降序</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>总星数</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星数</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>落哪条产线</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>可吸收形式</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>许可类型</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>是否新发现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>总星数</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星来源</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>日均涨星</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>区间涨星</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>区间天数</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>原始描述</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>许可证</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>语言</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>许可证</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>许可类型</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>可吸收形式</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>落哪条产线</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>能做什么</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>原始描述</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>证据</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>是否新发现</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -5148,62 +5388,68 @@
           <t>jub0t/Concat</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>提供免费且开源的视频编辑替代品</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>https://github.com/jub0t/Concat</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Free &amp; Open-Source CapCut replacement</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>MPL-2.0</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>视频产线</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>提供免费且开源的视频编辑替代品</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -5254,62 +5500,68 @@
           <t>liyue-aigc/seedance-2-5-video-director</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>https://github.com/liyue-aigc/seedance-2-5-video-director</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>16.93</v>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Seedance 2.5 视频导演 Skill</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>视频产线</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -5372,21 +5624,21 @@
   <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
@@ -5401,84 +5653,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>可用在【AI免费池】的候选 · 共 5 个 · 按日均涨星降序</t>
+          <t>可用在【AI免费池】的候选 · 共 5 个 · 按周涨星降序</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>总星数</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星数</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>落哪条产线</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>可吸收形式</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>许可类型</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>是否新发现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>总星数</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星来源</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>日均涨星</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>区间涨星</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>区间天数</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>原始描述</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>许可证</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>语言</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>许可证</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>许可类型</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>可吸收形式</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>落哪条产线</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>能做什么</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>原始描述</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>证据</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>是否新发现</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -5533,62 +5785,68 @@
           <t>21st-dev/magic-mcp</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>5775</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>https://github.com/21st-dev/magic-mcp</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>5775</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>10.31</v>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>It's like v0, but in your Cursor / Claude Code / Windsurf</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -5639,62 +5897,68 @@
           <t>budtmo/docker-android</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>15799</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>提供 Android 在 Docker 中的解决方案，支持视频录制和 MCP 服务器</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>https://github.com/budtmo/docker-android</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>15799</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>4.46</v>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>提供 Android 在 Docker 中的解决方案，支持视频录制和 MCP 服务器</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -5745,62 +6009,68 @@
           <t>ZeKaiNie/universal-examprep-skill</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>277</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude Agent Skill 的考试冲刺教练功能</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>https://github.com/ZeKaiNie/universal-examprep-skill</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="D5" s="5" t="n">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>3.96</v>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Last-night exam-cram coach as a Claude Agent Skill</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude Agent Skill 的考试冲刺教练功能</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -5851,62 +6121,68 @@
           <t>yushui2022/MathModel-Skill</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>https://github.com/yushui2022/MathModel-Skill</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>332</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>1.54</v>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Agent-native mathematical modeling workflow skills</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -5953,62 +6229,68 @@
           <t>VkRainB/ccMesh</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>AI免费池</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>https://github.com/VkRainB/ccMesh</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code / Codex local AI proxy gateway desktop app</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Rust</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>AI免费池</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -6071,21 +6353,21 @@
   <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
@@ -6100,84 +6382,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>可用在【未归类】的候选 · 共 15 个 · 按日均涨星降序</t>
+          <t>可用在【未归类】的候选 · 共 15 个 · 按周涨星降序</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>总星数</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星数</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>落哪条产线</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>可吸收形式</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>许可类型</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>是否新发现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>链接</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>总星数</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>周涨星来源</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>日均涨星</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>区间涨星</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>区间天数</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>原始描述</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>许可证</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>语言</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>许可证</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>许可类型</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>可吸收形式</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>落哪条产线</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>能做什么</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>原始描述</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>证据</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>是否新发现</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -6232,58 +6514,64 @@
           <t>subsy/skill-cabinet</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Skill 展示柜</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>https://github.com/subsy/skill-cabinet</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>328</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>skill-cabinet</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Skill 展示柜</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>skill-cabinet</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -6330,60 +6618,66 @@
           <t>sindresorhus/awesome-nodejs</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="n">
+        <v>66678</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>提供 Node.js 包和资源的列表</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>https://github.com/sindresorhus/awesome-nodejs</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>66678</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>15.03</v>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Delightful Node.js packages and resources</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>提供 Node.js 包和资源的列表</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Delightful Node.js packages and resources</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6432,60 +6726,66 @@
           <t>steven2358/awesome-generative-ai</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>12552</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>提供现代生成式人工智能项目和服务的精选列表</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>https://github.com/steven2358/awesome-generative-ai</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>12552</v>
-      </c>
-      <c r="D5" s="5" t="n">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>提供现代生成式人工智能项目和服务的精选列表</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6534,62 +6834,68 @@
           <t>edoardottt/awesome-hacker-search-engines</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>11117</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>https://github.com/edoardottt/awesome-hacker-search-engines</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>11117</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>7.24</v>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Shell</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -6640,62 +6946,68 @@
           <t>Rzna-5559/Mrite</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>445</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>内置 Skill 的数模智能体</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>https://github.com/Rzna-5559/Mrite</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>445</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>5.24</v>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>全网最强数模智能体内置Skill</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>全网最强数模智能体内置Skill</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>TeX</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>内置 Skill 的数模智能体</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>全网最强数模智能体内置Skill</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>全网最强数模智能体内置Skill</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -6742,62 +7054,68 @@
           <t>scaccogatto/okf-skills</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>353</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>https://github.com/scaccogatto/okf-skills</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>353</v>
-      </c>
-      <c r="D8" s="5" t="n">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>4.41</v>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles.</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles.</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -6848,62 +7166,68 @@
           <t>lgazo/drawio-mcp-server</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) 服务器</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>https://github.com/lgazo/drawio-mcp-server</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>1455</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>2.92</v>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) Server</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Draw.io Model Context Protocol (MCP) Server</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) 服务器</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -6950,60 +7274,66 @@
           <t>Calinou/awesome-godot</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="n">
+        <v>10677</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Godot 引擎插件、脚本和附加组件列表</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>https://github.com/Calinou/awesome-godot</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>10677</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>2.57</v>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>Godot 引擎插件、脚本和附加组件列表</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -7052,62 +7382,68 @@
           <t>Taxuspt/garmin_mcp</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>访问 Garmin 数据的 MCP 服务器</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>https://github.com/Taxuspt/garmin_mcp</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1102</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>2.03</v>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>MCP server to access Garmin data</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>MCP server to access Garmin data</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MCP服务</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>访问 Garmin 数据的 MCP 服务器</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -7154,62 +7490,68 @@
           <t>realZillionX/InspireSkill</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>https://github.com/realZillionX/InspireSkill</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>201</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>1.49</v>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>Python</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -7256,62 +7598,68 @@
           <t>dodolalorc/astro-navfolio</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>提供基于 Astro 的个人发布主题</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>https://github.com/dodolalorc/astro-navfolio</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>A serene Astro theme for personal publishing</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Astro</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>架构参考</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>提供基于 Astro 的个人发布主题</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>A serene Astro theme for personal publishing</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -7362,62 +7710,68 @@
           <t>81NewArk/AntiCAP-WebApi</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>提供基于 AntiCAP 开发的多类型验证码识别网站</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>https://github.com/81NewArk/AntiCAP-WebApi</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>366</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>基于AntiCAP开发的多类型验证码识别网站</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>HTML</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>提供基于 AntiCAP 开发的多类型验证码识别网站</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -7464,60 +7818,66 @@
           <t>mikalv/awesome-qt-qml</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="n">
+        <v>2605</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Qt 和 QML 库、资源、项目列表</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>https://github.com/mikalv/awesome-qt-qml</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>2605</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>Qt 和 QML 库、资源、项目列表</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -7566,62 +7926,68 @@
           <t>curiositech/some_claude_skills</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>提供 Claude skills，简化生活操作</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>https://github.com/curiositech/some_claude_skills</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>209</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>0.72</v>
       </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Claude skills that make my life easier.</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Claude skills that make my life easier.</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>提供 Claude skills，简化生活操作</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -7668,60 +8034,66 @@
           <t>tmcw/awesome-geojson</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="n">
+        <v>2535</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON 工具库，简化操作</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>https://github.com/tmcw/awesome-geojson</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>2535</v>
-      </c>
-      <c r="D17" s="5" t="n">
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON utilities that will make your life easier.</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>GeoJSON utilities that will make your life easier.</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>CC0-1.0</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>未归类</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON 工具库，简化操作</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
           <t>否</t>

--- a/reports/arsenal/军火榜_2026-09-02.xlsx
+++ b/reports/arsenal/军火榜_2026-09-02.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$X$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,13 +476,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -490,19 +490,17 @@
     <col width="46" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,7 +528,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>功能(详细)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,71 +568,61 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>原始描述</t>
+          <t>许可证</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>证据</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>许可证</t>
+          <t>军火库已有</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>已蒸馏</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>军火库已有</t>
+          <t>话题标签</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>已蒸馏</t>
+          <t>创建日期</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>话题标签</t>
+          <t>最后推送</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>创建日期</t>
+          <t>仓龄(天)</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>最后推送</t>
+          <t>命中查询数</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>仓龄(天)</t>
+          <t>发现维度</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>命中查询数</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>发现维度</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
           <t>发现查询式</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>subsy/skill-cabinet</t>
@@ -648,7 +636,8 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Skill 展示柜</t>
+          <t>Skill 展示柜
+【依据】skill-cabinet</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -684,61 +673,55 @@
       <c r="K3" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="L3" s="6" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>skill-cabinet</t>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>jub0t/Concat</t>
@@ -752,7 +735,8 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供免费且开源的视频编辑替代品</t>
+          <t>提供免费且开源的视频编辑替代品
+【原文】Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -788,69 +772,59 @@
       <c r="K4" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Free &amp; Open-Source CapCut replacement</t>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>MPL-2.0</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>audio-processor, auto-caption, automation, capcut, capcut-alternative, content-creation, cross-platform, desktop-app, ffmpeg, free-video-editor, non-linear-editor, offline-first</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>audio-processor, auto-caption, automation, capcut, capcut-alternative, content-creation, cross-platform, desktop-app, ffmpeg, free-video-editor, non-linear-editor, offline-first</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>topic:content-creation stars:&gt;1000 pushed:&gt;2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>liyue-aigc/seedance-2-5-video-director</t>
@@ -864,7 +838,8 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能</t>
+          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能
+【原文】Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -900,69 +875,59 @@
       <c r="K5" s="5" t="n">
         <v>16.93</v>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Seedance 2.5 视频导演 Skill</t>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>ai-video, codex-skill, dreamina, seedance, video-prompt</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>ai-video, codex-skill, dreamina, seedance, video-prompt</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="X5" s="6" t="inlineStr">
+      <c r="V5" s="6" t="inlineStr">
         <is>
           <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>sindresorhus/awesome-nodejs</t>
@@ -976,7 +941,8 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供 Node.js 包和资源的列表</t>
+          <t>提供 Node.js 包和资源的列表
+【原文】:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1012,65 +978,55 @@
       <c r="K6" s="5" t="n">
         <v>15.03</v>
       </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>Delightful Node.js packages and resources</t>
-        </is>
-      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, javascript, list, node, nodejs</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, javascript, list, node, nodejs</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
           <t>2014-07-11</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="S6" s="3" t="n">
         <v>4436</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X6" s="6" t="inlineStr">
+      <c r="V6" s="6" t="inlineStr">
         <is>
           <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>21st-dev/magic-mcp</t>
@@ -1084,7 +1040,8 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中</t>
+          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中
+【原文】It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1120,69 +1077,59 @@
       <c r="K7" s="5" t="n">
         <v>10.31</v>
       </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>It's like v0, but in your Cursor / Claude Code / Windsurf</t>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>21st, claude, cursor, mcp, model-context-protocol, react, tailwindcss, ui-components</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>21st, claude, cursor, mcp, model-context-protocol, react, tailwindcss, ui-components</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="S7" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="X7" s="6" t="inlineStr">
+      <c r="V7" s="6" t="inlineStr">
         <is>
           <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>steven2358/awesome-generative-ai</t>
@@ -1196,7 +1143,8 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供现代生成式人工智能项目和服务的精选列表</t>
+          <t>提供现代生成式人工智能项目和服务的精选列表
+【原文】A curated list of modern Generative Artificial Intelligence projects and services</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1232,65 +1180,55 @@
       <c r="K8" s="5" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of modern Generative Artificial Intelligence projects and services</t>
-        </is>
-      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>ai, artificial-intelligence, awesome, awesome-list, generative-ai, generative-art, large-language-models, llm</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>ai, artificial-intelligence, awesome, awesome-list, generative-ai, generative-art, large-language-models, llm</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
           <t>2022-10-20</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="S8" s="3" t="n">
         <v>1413</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X8" s="6" t="inlineStr">
+      <c r="V8" s="6" t="inlineStr">
         <is>
           <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>edoardottt/awesome-hacker-search-engines</t>
@@ -1304,7 +1242,8 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表
+【原文】A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1340,69 +1279,59 @@
       <c r="K9" s="5" t="n">
         <v>7.24</v>
       </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表</t>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, awesome-lists, bugbounty, cve, dns, exploit, hacking, hacking-tools, hacktoberfest, osint, osint-tool</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, awesome-lists, bugbounty, cve, dns, exploit, hacking, hacking-tools, hacktoberfest, osint, osint-tool</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
           <t>2022-06-20</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="S9" s="3" t="n">
         <v>1535</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X9" s="6" t="inlineStr">
+      <c r="V9" s="6" t="inlineStr">
         <is>
           <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Rzna-5559/Mrite</t>
@@ -1416,7 +1345,8 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>内置 Skill 的数模智能体</t>
+          <t>内置 Skill 的数模智能体
+【原文】全网最强数模智能体内置Skill</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1452,65 +1382,55 @@
       <c r="K10" s="5" t="n">
         <v>5.24</v>
       </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>全网最强数模智能体内置Skill</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>全网最强数模智能体内置Skill</t>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>TeX</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>TeX</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="X10" s="6" t="inlineStr">
+      <c r="V10" s="6" t="inlineStr">
         <is>
           <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>budtmo/docker-android</t>
@@ -1524,7 +1444,8 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供 Android 在 Docker 中的解决方案，支持视频录制和 MCP 服务器</t>
+          <t>提供 Android 在 Docker 中的解决方案，支持视频录制和 MCP 服务器
+【原文】Android in docker solution with noVNC supported, video recording and mcp server</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1560,69 +1481,59 @@
       <c r="K11" s="5" t="n">
         <v>4.46</v>
       </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Android in docker solution with noVNC supported, video recording and mcp server</t>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>android, android-emulator, aws, azure, cloud, docker, docker-android, emulator, gcp, genymotion, jenkins, kubernetes</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>android, android-emulator, aws, azure, cloud, docker, docker-android, emulator, gcp, genymotion, jenkins, kubernetes</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
           <t>2016-12-22</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="S11" s="3" t="n">
         <v>3541</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="T11" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>scaccogatto/okf-skills</t>
@@ -1636,7 +1547,8 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包</t>
+          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包
+【原文】The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1672,69 +1584,59 @@
       <c r="K12" s="5" t="n">
         <v>4.41</v>
       </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles.</t>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai-agents, claude-code, claude-code-plugin, developer-tools, knowledge-graph, knowledge-management, llm-tools, markdown, mcp, okf, open-knowledge-format</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>agent-skills, ai-agents, claude-code, claude-code-plugin, developer-tools, knowledge-graph, knowledge-management, llm-tools, markdown, mcp, okf, open-knowledge-format</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="S12" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="T12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W12" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X12" s="6" t="inlineStr">
+      <c r="V12" s="6" t="inlineStr">
         <is>
           <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>ZeKaiNie/universal-examprep-skill</t>
@@ -1748,7 +1650,8 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Agent Skill 的考试冲刺教练功能</t>
+          <t>提供 Claude Agent Skill 的考试冲刺教练功能
+【原文】Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1784,69 +1687,59 @@
       <c r="K13" s="5" t="n">
         <v>3.96</v>
       </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>Last-night exam-cram coach as a Claude Agent Skill</t>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>agent-skill, ai-tutor, anthropic, anti-hallucination, claude, claude-code, claude-skill, cram, edtech, education, exam-prep, llm</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>agent-skill, ai-tutor, anthropic, anti-hallucination, claude, claude-code, claude-skill, cram, edtech, education, exam-prep, llm</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="S13" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X13" s="6" t="inlineStr">
+      <c r="V13" s="6" t="inlineStr">
         <is>
           <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>lgazo/drawio-mcp-server</t>
@@ -1860,7 +1753,8 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Draw.io Model Context Protocol (MCP) 服务器</t>
+          <t>Draw.io Model Context Protocol (MCP) 服务器
+【原文】Draw.io Model Context Protocol (MCP) Server</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1896,65 +1790,55 @@
       <c r="K14" s="5" t="n">
         <v>2.92</v>
       </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>Draw.io Model Context Protocol (MCP) Server</t>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="S14" s="3" t="n">
         <v>499</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W14" s="3" t="inlineStr">
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X14" s="6" t="inlineStr">
+      <c r="V14" s="6" t="inlineStr">
         <is>
           <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Calinou/awesome-godot</t>
@@ -1968,7 +1852,8 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Godot 引擎插件、脚本和附加组件列表</t>
+          <t>Godot 引擎插件、脚本和附加组件列表
+【原文】A curated list of free/libre plugins, scripts and add-ons for Godot</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2004,65 +1889,55 @@
       <c r="K15" s="5" t="n">
         <v>2.57</v>
       </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of free/libre plugins, scripts and add-ons for Godot</t>
-        </is>
-      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, game-development, godot, godot-engine</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, game-development, godot, godot-engine</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
           <t>2015-04-12</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="S15" s="3" t="n">
         <v>4161</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W15" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X15" s="6" t="inlineStr">
+      <c r="V15" s="6" t="inlineStr">
         <is>
           <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Taxuspt/garmin_mcp</t>
@@ -2076,7 +1951,8 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>访问 Garmin 数据的 MCP 服务器</t>
+          <t>访问 Garmin 数据的 MCP 服务器
+【原文】MCP server to access Garmin data</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2112,65 +1988,55 @@
       <c r="K16" s="5" t="n">
         <v>2.03</v>
       </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>MCP server to access Garmin data</t>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="S16" s="3" t="n">
         <v>543</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="T16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W16" s="3" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X16" s="6" t="inlineStr">
+      <c r="V16" s="6" t="inlineStr">
         <is>
           <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>yushui2022/MathModel-Skill</t>
@@ -2184,7 +2050,8 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等</t>
+          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等
+【原文】Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2220,65 +2087,55 @@
       <c r="K17" s="5" t="n">
         <v>1.54</v>
       </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>Agent-native mathematical modeling workflow skills</t>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="S17" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W17" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X17" s="6" t="inlineStr">
+      <c r="V17" s="6" t="inlineStr">
         <is>
           <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>realZillionX/InspireSkill</t>
@@ -2292,7 +2149,8 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作</t>
+          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作
+【原文】启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2328,65 +2186,55 @@
       <c r="K18" s="5" t="n">
         <v>1.49</v>
       </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。</t>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="S18" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="T18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W18" s="3" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X18" s="6" t="inlineStr">
+      <c r="V18" s="6" t="inlineStr">
         <is>
           <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>VkRainB/ccMesh</t>
@@ -2400,7 +2248,8 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序</t>
+          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序
+【原文】Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2436,69 +2285,59 @@
       <c r="K19" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>Claude Code / Codex local AI proxy gateway desktop app</t>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>claude, desktop-app, gateway, llm, local-proxy, protocol-conversion, tauri2</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>claude, desktop-app, gateway, llm, local-proxy, protocol-conversion, tauri2</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="S19" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="T19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W19" s="3" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="X19" s="6" t="inlineStr">
+      <c r="V19" s="6" t="inlineStr">
         <is>
           <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>dodolalorc/astro-navfolio</t>
@@ -2512,7 +2351,8 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>提供基于 Astro 的个人发布主题</t>
+          <t>提供基于 Astro 的个人发布主题
+【原文】🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2548,69 +2388,59 @@
       <c r="K20" s="5" t="n">
         <v>0.89</v>
       </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>A serene Astro theme for personal publishing</t>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Astro</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Astro</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>astro, blog-theme</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>astro, blog-theme</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="S20" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="T20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W20" s="3" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="X20" s="6" t="inlineStr">
+      <c r="V20" s="6" t="inlineStr">
         <is>
           <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>81NewArk/AntiCAP-WebApi</t>
@@ -2624,7 +2454,8 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供基于 AntiCAP 开发的多类型验证码识别网站</t>
+          <t>提供基于 AntiCAP 开发的多类型验证码识别网站
+【原文】基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2660,65 +2491,55 @@
       <c r="K21" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>基于AntiCAP开发的多类型验证码识别网站</t>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="S21" s="3" t="n">
         <v>460</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="T21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W21" s="3" t="inlineStr">
+      <c r="U21" s="3" t="inlineStr">
         <is>
           <t>chinese</t>
         </is>
       </c>
-      <c r="X21" s="6" t="inlineStr">
+      <c r="V21" s="6" t="inlineStr">
         <is>
           <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>mikalv/awesome-qt-qml</t>
@@ -2732,7 +2553,8 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Qt 和 QML 库、资源、项目列表</t>
+          <t>Qt 和 QML 库、资源、项目列表
+【原文】A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2768,65 +2590,55 @@
       <c r="K22" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
-        </is>
-      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, cpp, javascript, qml, qml-bindings, qpm, qt, qt-quick, qt4, qt5, qtcreator</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, cpp, javascript, qml, qml-bindings, qpm, qt, qt-quick, qt4, qt5, qtcreator</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
           <t>2017-06-25</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="S22" s="3" t="n">
         <v>3356</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W22" s="3" t="inlineStr">
+      <c r="U22" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X22" s="6" t="inlineStr">
+      <c r="V22" s="6" t="inlineStr">
         <is>
           <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>curiositech/some_claude_skills</t>
@@ -2840,7 +2652,8 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude skills，简化生活操作</t>
+          <t>提供 Claude skills，简化生活操作
+【原文】Claude skills that make my life easier.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2876,65 +2689,55 @@
       <c r="K23" s="5" t="n">
         <v>0.72</v>
       </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>Claude skills that make my life easier.</t>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>否</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="U23" s="3" t="n">
+      <c r="S23" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="T23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W23" s="3" t="inlineStr">
+      <c r="U23" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X23" s="6" t="inlineStr">
+      <c r="V23" s="6" t="inlineStr">
         <is>
           <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>tmcw/awesome-geojson</t>
@@ -2948,7 +2751,8 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>GeoJSON 工具库，简化操作</t>
+          <t>GeoJSON 工具库，简化操作
+【原文】GeoJSON utilities that will make your life easier.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2984,68 +2788,58 @@
       <c r="K24" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>GeoJSON utilities that will make your life easier.</t>
-        </is>
-      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>CC0-1.0</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr"/>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>awesome, awesome-list, geojson, list</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, geojson, list</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
           <t>2015-05-28</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U24" s="3" t="n">
+      <c r="S24" s="3" t="n">
         <v>4115</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="T24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="W24" s="3" t="inlineStr">
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="X24" s="6" t="inlineStr">
+      <c r="V24" s="6" t="inlineStr">
         <is>
           <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X24"/>
+  <autoFilter ref="A2:V24"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
